--- a/测试文件/原料数据模板.xlsx
+++ b/测试文件/原料数据模板.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="宋体"/>
       <family val="2"/>
@@ -59,6 +59,17 @@
       <name val="宋体"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -98,7 +109,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -112,11 +123,25 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -136,6 +161,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -547,902 +578,902 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>原料名称</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>价格(元/kg)</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>精粗类型</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>猪消化能MC/Kg</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>禽代谢能MC/Kg</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>综合净能(牛)MC/Kg</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>羊消化能MC/Kg</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>消化能(其他)MC/Kg</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>粗蛋白%</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>粗脂肪%</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>粗纤维%</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>粗灰分%</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="M1" s="9" t="inlineStr">
         <is>
           <t>钙%</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="N1" s="9" t="inlineStr">
         <is>
           <t>总磷%</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="O1" s="9" t="inlineStr">
         <is>
           <t>非植酸磷%</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="P1" s="9" t="inlineStr">
         <is>
           <t>食盐%</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="Q1" s="9" t="inlineStr">
         <is>
           <t>赖氨酸%</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="R1" s="9" t="inlineStr">
         <is>
           <t>蛋氨酸%</t>
         </is>
       </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="S1" s="9" t="inlineStr">
         <is>
           <t>蛋胱氨酸%</t>
         </is>
       </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="T1" s="9" t="inlineStr">
         <is>
           <t>胱氨酸%</t>
         </is>
       </c>
-      <c r="U1" s="3" t="inlineStr">
+      <c r="U1" s="9" t="inlineStr">
         <is>
           <t>色氨酸%</t>
         </is>
       </c>
-      <c r="V1" s="3" t="inlineStr">
+      <c r="V1" s="9" t="inlineStr">
         <is>
           <t>苏氨酸%</t>
         </is>
       </c>
-      <c r="W1" s="3" t="inlineStr">
+      <c r="W1" s="9" t="inlineStr">
         <is>
           <t>异亮氨酸%</t>
         </is>
       </c>
-      <c r="X1" s="3" t="inlineStr">
+      <c r="X1" s="9" t="inlineStr">
         <is>
           <t>亮氨酸%</t>
         </is>
       </c>
-      <c r="Y1" s="3" t="inlineStr">
+      <c r="Y1" s="9" t="inlineStr">
         <is>
           <t>缬氨酸%</t>
         </is>
       </c>
-      <c r="Z1" s="3" t="inlineStr">
+      <c r="Z1" s="9" t="inlineStr">
         <is>
           <t>苯丙氨酸%</t>
         </is>
       </c>
-      <c r="AA1" s="3" t="inlineStr">
+      <c r="AA1" s="9" t="inlineStr">
         <is>
           <t>干物质%</t>
         </is>
       </c>
-      <c r="AB1" s="3" t="inlineStr">
+      <c r="AB1" s="9" t="inlineStr">
         <is>
           <t>中性洗涤纤维%</t>
         </is>
       </c>
-      <c r="AC1" s="3" t="inlineStr">
+      <c r="AC1" s="9" t="inlineStr">
         <is>
           <t>酸性洗涤纤维%</t>
         </is>
       </c>
-      <c r="AD1" s="3" t="inlineStr">
+      <c r="AD1" s="9" t="inlineStr">
         <is>
           <t>钠%</t>
         </is>
       </c>
-      <c r="AE1" s="3" t="inlineStr">
+      <c r="AE1" s="9" t="inlineStr">
         <is>
           <t>钾%</t>
         </is>
       </c>
-      <c r="AF1" s="3" t="inlineStr">
+      <c r="AF1" s="9" t="inlineStr">
         <is>
           <t>氯%</t>
         </is>
       </c>
-      <c r="AG1" s="3" t="inlineStr">
+      <c r="AG1" s="9" t="inlineStr">
         <is>
           <t>亚油酸%</t>
         </is>
       </c>
-      <c r="AH1" s="6" t="inlineStr">
+      <c r="AH1" s="9" t="inlineStr">
         <is>
           <t>黄曲霉素μg/kg</t>
         </is>
       </c>
-      <c r="AI1" s="6" t="inlineStr">
+      <c r="AI1" s="9" t="inlineStr">
         <is>
           <t>呕吐毒素μg/kg</t>
         </is>
       </c>
-      <c r="AJ1" s="6" t="inlineStr">
+      <c r="AJ1" s="9" t="inlineStr">
         <is>
           <t>玉米赤霉烯酮μg/kg</t>
         </is>
       </c>
-      <c r="AK1" s="6" t="inlineStr">
+      <c r="AK1" s="9" t="inlineStr">
         <is>
           <t>T-2毒素μg/kg</t>
         </is>
       </c>
-      <c r="AL1" s="6" t="inlineStr">
+      <c r="AL1" s="9" t="inlineStr">
         <is>
           <t>赭曲霉毒素μg/kg</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>玉米[1级]</t>
         </is>
       </c>
-      <c r="B2" s="7" t="n">
+      <c r="B2" s="10" t="n">
         <v>1.6</v>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>精料</t>
         </is>
       </c>
-      <c r="D2" s="7" t="n">
+      <c r="D2" s="10" t="n">
         <v>3.32</v>
       </c>
-      <c r="E2" s="7" t="n">
+      <c r="E2" s="10" t="n">
         <v>3.36</v>
       </c>
-      <c r="F2" s="7" t="n"/>
-      <c r="G2" s="7" t="n"/>
-      <c r="H2" s="7" t="n"/>
-      <c r="I2" s="7" t="n">
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="10" t="n"/>
+      <c r="H2" s="10" t="n"/>
+      <c r="I2" s="10" t="n">
         <v>7.8</v>
       </c>
-      <c r="J2" s="7" t="n">
+      <c r="J2" s="10" t="n">
         <v>3.5</v>
       </c>
-      <c r="K2" s="7" t="n">
+      <c r="K2" s="10" t="n">
         <v>1.6</v>
       </c>
-      <c r="L2" s="7" t="n">
+      <c r="L2" s="10" t="n">
         <v>1.3</v>
       </c>
-      <c r="M2" s="7" t="n">
+      <c r="M2" s="10" t="n">
         <v>0.02</v>
       </c>
-      <c r="N2" s="7" t="n">
+      <c r="N2" s="10" t="n">
         <v>0.27</v>
       </c>
-      <c r="O2" s="7" t="n">
+      <c r="O2" s="10" t="n">
         <v>0.12</v>
       </c>
-      <c r="P2" s="7" t="n"/>
-      <c r="Q2" s="7" t="n">
+      <c r="P2" s="10" t="n"/>
+      <c r="Q2" s="10" t="n">
         <v>0.23</v>
       </c>
-      <c r="R2" s="7" t="n">
+      <c r="R2" s="10" t="n">
         <v>0.15</v>
       </c>
-      <c r="S2" s="7" t="n">
+      <c r="S2" s="10" t="n">
         <v>0.06</v>
       </c>
-      <c r="T2" s="7" t="n">
+      <c r="T2" s="10" t="n">
         <v>0.04</v>
       </c>
-      <c r="U2" s="7" t="n">
+      <c r="U2" s="10" t="n">
         <v>0.09</v>
       </c>
-      <c r="V2" s="7" t="n">
+      <c r="V2" s="10" t="n">
         <v>0.12</v>
       </c>
-      <c r="W2" s="7" t="n">
+      <c r="W2" s="10" t="n">
         <v>0.13</v>
       </c>
-      <c r="X2" s="7" t="n">
+      <c r="X2" s="10" t="n">
         <v>0.08</v>
       </c>
-      <c r="Y2" s="7" t="n">
+      <c r="Y2" s="10" t="n">
         <v>0.08</v>
       </c>
-      <c r="Z2" s="7" t="n">
+      <c r="Z2" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="AA2" s="7" t="n">
+      <c r="AA2" s="10" t="n">
         <v>86</v>
       </c>
-      <c r="AB2" s="7" t="n">
+      <c r="AB2" s="10" t="n">
         <v>86</v>
       </c>
-      <c r="AC2" s="7" t="n"/>
-      <c r="AD2" s="7" t="n"/>
-      <c r="AE2" s="7" t="n">
+      <c r="AC2" s="10" t="n"/>
+      <c r="AD2" s="10" t="n"/>
+      <c r="AE2" s="10" t="n">
         <v>0.03</v>
       </c>
-      <c r="AF2" s="7" t="n">
+      <c r="AF2" s="10" t="n">
         <v>0.38</v>
       </c>
-      <c r="AG2" s="7" t="n">
+      <c r="AG2" s="10" t="n">
         <v>0.04</v>
       </c>
-      <c r="AH2" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" s="7" t="n">
+      <c r="AH2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>大豆粕[2级]</t>
         </is>
       </c>
-      <c r="B3" s="8" t="n">
+      <c r="B3" s="10" t="n">
         <v>2.1</v>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>精料</t>
         </is>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="D3" s="10" t="n">
         <v>2.39</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="10" t="n">
         <v>2.31</v>
       </c>
-      <c r="F3" s="8" t="n"/>
-      <c r="G3" s="8" t="n"/>
-      <c r="H3" s="8" t="n"/>
-      <c r="I3" s="8" t="n">
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="10" t="n"/>
+      <c r="I3" s="10" t="n">
         <v>44.2</v>
       </c>
-      <c r="J3" s="8" t="n">
+      <c r="J3" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="K3" s="8" t="n">
+      <c r="K3" s="10" t="n">
         <v>5.9</v>
       </c>
-      <c r="L3" s="8" t="n">
+      <c r="L3" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="M3" s="8" t="n">
+      <c r="M3" s="10" t="n">
         <v>0.32</v>
       </c>
-      <c r="N3" s="8" t="n">
+      <c r="N3" s="10" t="n">
         <v>0.61</v>
       </c>
-      <c r="O3" s="8" t="n">
+      <c r="O3" s="10" t="n">
         <v>0.18</v>
       </c>
-      <c r="P3" s="8" t="n"/>
-      <c r="Q3" s="8" t="n">
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n">
         <v>2.68</v>
       </c>
-      <c r="R3" s="8" t="n">
+      <c r="R3" s="10" t="n">
         <v>0.59</v>
       </c>
-      <c r="S3" s="8" t="n">
+      <c r="S3" s="10" t="n">
         <v>0.65</v>
       </c>
-      <c r="T3" s="8" t="n">
+      <c r="T3" s="10" t="n">
         <v>0.39</v>
       </c>
-      <c r="U3" s="8" t="n">
+      <c r="U3" s="10" t="n">
         <v>0.57</v>
       </c>
-      <c r="V3" s="8" t="n">
+      <c r="V3" s="10" t="n">
         <v>1.71</v>
       </c>
-      <c r="W3" s="8" t="n">
+      <c r="W3" s="10" t="n">
         <v>2.2</v>
       </c>
-      <c r="X3" s="8" t="n">
+      <c r="X3" s="10" t="n">
         <v>2.4</v>
       </c>
-      <c r="Y3" s="8" t="n">
+      <c r="Y3" s="10" t="n">
         <v>2.5</v>
       </c>
-      <c r="Z3" s="8" t="n">
+      <c r="Z3" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="AA3" s="8" t="n">
+      <c r="AA3" s="10" t="n">
         <v>89</v>
       </c>
-      <c r="AB3" s="8" t="n">
+      <c r="AB3" s="10" t="n">
         <v>89</v>
       </c>
-      <c r="AC3" s="8" t="n">
+      <c r="AC3" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="AD3" s="8" t="n">
+      <c r="AD3" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="AE3" s="8" t="n">
+      <c r="AE3" s="10" t="n">
         <v>0.02</v>
       </c>
-      <c r="AF3" s="8" t="n">
+      <c r="AF3" s="10" t="n">
         <v>1.9</v>
       </c>
-      <c r="AG3" s="8" t="n">
+      <c r="AG3" s="10" t="n">
         <v>0.08</v>
       </c>
-      <c r="AH3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" s="8" t="n">
+      <c r="AH3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>小麦麸</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n">
+      <c r="B4" s="10" t="n">
         <v>1.55</v>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>精料</t>
         </is>
       </c>
-      <c r="D4" s="7" t="n">
+      <c r="D4" s="10" t="n">
         <v>1.36</v>
       </c>
-      <c r="E4" s="7" t="n">
+      <c r="E4" s="10" t="n">
         <v>1.56</v>
       </c>
-      <c r="F4" s="7" t="n"/>
-      <c r="G4" s="7" t="n"/>
-      <c r="H4" s="7" t="n"/>
-      <c r="I4" s="7" t="n">
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="10" t="n"/>
+      <c r="I4" s="10" t="n">
         <v>14.3</v>
       </c>
-      <c r="J4" s="7" t="n">
+      <c r="J4" s="10" t="n">
         <v>3.8</v>
       </c>
-      <c r="K4" s="7" t="n">
+      <c r="K4" s="10" t="n">
         <v>6.8</v>
       </c>
-      <c r="L4" s="7" t="n">
+      <c r="L4" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="M4" s="7" t="n">
+      <c r="M4" s="10" t="n">
         <v>0.14</v>
       </c>
-      <c r="N4" s="7" t="n">
+      <c r="N4" s="10" t="n">
         <v>0.93</v>
       </c>
-      <c r="O4" s="7" t="n">
+      <c r="O4" s="10" t="n">
         <v>0.24</v>
       </c>
-      <c r="P4" s="7" t="n"/>
-      <c r="Q4" s="7" t="n">
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="10" t="n">
         <v>0.53</v>
       </c>
-      <c r="R4" s="7" t="n">
+      <c r="R4" s="10" t="n">
         <v>0.12</v>
       </c>
-      <c r="S4" s="7" t="n">
+      <c r="S4" s="10" t="n">
         <v>0.38</v>
       </c>
-      <c r="T4" s="7" t="n">
+      <c r="T4" s="10" t="n">
         <v>0.26</v>
       </c>
-      <c r="U4" s="7" t="n">
+      <c r="U4" s="10" t="n">
         <v>0.18</v>
       </c>
-      <c r="V4" s="7" t="n">
+      <c r="V4" s="10" t="n">
         <v>0.39</v>
       </c>
-      <c r="W4" s="7" t="n">
+      <c r="W4" s="10" t="n">
         <v>0.48</v>
       </c>
-      <c r="X4" s="7" t="n">
+      <c r="X4" s="10" t="n">
         <v>0.49</v>
       </c>
-      <c r="Y4" s="7" t="n">
+      <c r="Y4" s="10" t="n">
         <v>0.76</v>
       </c>
-      <c r="Z4" s="7" t="n">
+      <c r="Z4" s="10" t="n">
         <v>0.57</v>
       </c>
-      <c r="AA4" s="7" t="n">
+      <c r="AA4" s="10" t="n">
         <v>87</v>
       </c>
-      <c r="AB4" s="7" t="n">
+      <c r="AB4" s="10" t="n">
         <v>87</v>
       </c>
-      <c r="AC4" s="7" t="n">
+      <c r="AC4" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="AD4" s="7" t="n">
+      <c r="AD4" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="AE4" s="7" t="n">
+      <c r="AE4" s="10" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AF4" s="7" t="n">
+      <c r="AF4" s="10" t="n">
         <v>1.2</v>
       </c>
-      <c r="AG4" s="7" t="n">
+      <c r="AG4" s="10" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AH4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" s="7" t="n">
+      <c r="AH4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>进口鱼粉</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="10" t="n">
         <v>4.8</v>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>精料</t>
         </is>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="10" t="n">
         <v>2.82</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="10" t="n">
         <v>2.8</v>
       </c>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
-      <c r="H5" s="8" t="n"/>
-      <c r="I5" s="8" t="n">
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="10" t="n"/>
+      <c r="I5" s="10" t="n">
         <v>64.5</v>
       </c>
-      <c r="J5" s="8" t="n">
+      <c r="J5" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="K5" s="8" t="n">
+      <c r="K5" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="L5" s="8" t="n">
+      <c r="L5" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="M5" s="8" t="n">
+      <c r="M5" s="10" t="n">
         <v>4.04</v>
       </c>
-      <c r="N5" s="8" t="n">
+      <c r="N5" s="10" t="n">
         <v>2.9</v>
       </c>
-      <c r="O5" s="8" t="n">
+      <c r="O5" s="10" t="n">
         <v>2.6</v>
       </c>
-      <c r="P5" s="8" t="n"/>
-      <c r="Q5" s="8" t="n">
+      <c r="P5" s="10" t="n"/>
+      <c r="Q5" s="10" t="n">
         <v>4.72</v>
       </c>
-      <c r="R5" s="8" t="n">
+      <c r="R5" s="10" t="n">
         <v>1.64</v>
       </c>
-      <c r="S5" s="8" t="n">
+      <c r="S5" s="10" t="n">
         <v>1.38</v>
       </c>
-      <c r="T5" s="8" t="n">
+      <c r="T5" s="10" t="n">
         <v>0.74</v>
       </c>
-      <c r="U5" s="8" t="n">
+      <c r="U5" s="10" t="n">
         <v>0.7</v>
       </c>
-      <c r="V5" s="8" t="n">
+      <c r="V5" s="10" t="n">
         <v>2.57</v>
       </c>
-      <c r="W5" s="8" t="n">
+      <c r="W5" s="10" t="n">
         <v>2.8</v>
       </c>
-      <c r="X5" s="8" t="n">
+      <c r="X5" s="10" t="n">
         <v>2.8</v>
       </c>
-      <c r="Y5" s="8" t="n">
+      <c r="Y5" s="10" t="n">
         <v>2.9</v>
       </c>
-      <c r="Z5" s="8" t="n">
+      <c r="Z5" s="10" t="n">
         <v>3.2</v>
       </c>
-      <c r="AA5" s="8" t="n">
+      <c r="AA5" s="10" t="n">
         <v>90</v>
       </c>
-      <c r="AB5" s="8" t="n">
+      <c r="AB5" s="10" t="n">
         <v>90</v>
       </c>
-      <c r="AC5" s="8" t="n"/>
-      <c r="AD5" s="8" t="n"/>
-      <c r="AE5" s="8" t="n">
+      <c r="AC5" s="10" t="n"/>
+      <c r="AD5" s="10" t="n"/>
+      <c r="AE5" s="10" t="n">
         <v>0.97</v>
       </c>
-      <c r="AF5" s="8" t="n">
+      <c r="AF5" s="10" t="n">
         <v>0.61</v>
       </c>
-      <c r="AG5" s="8" t="n">
+      <c r="AG5" s="10" t="n">
         <v>0.65</v>
       </c>
-      <c r="AH5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" s="8" t="n">
+      <c r="AH5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>石粉</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>矿物质饲料</t>
         </is>
       </c>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="7" t="n"/>
-      <c r="J6" s="7" t="n"/>
-      <c r="K6" s="7" t="n"/>
-      <c r="L6" s="7" t="n"/>
-      <c r="M6" s="7" t="n">
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="10" t="n"/>
+      <c r="F6" s="10" t="n"/>
+      <c r="G6" s="10" t="n"/>
+      <c r="H6" s="10" t="n"/>
+      <c r="I6" s="10" t="n"/>
+      <c r="J6" s="10" t="n"/>
+      <c r="K6" s="10" t="n"/>
+      <c r="L6" s="10" t="n"/>
+      <c r="M6" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="N6" s="7" t="n"/>
-      <c r="O6" s="7" t="n"/>
-      <c r="P6" s="7" t="n"/>
-      <c r="Q6" s="7" t="n"/>
-      <c r="R6" s="7" t="n"/>
-      <c r="S6" s="7" t="n"/>
-      <c r="T6" s="7" t="n"/>
-      <c r="U6" s="7" t="n"/>
-      <c r="V6" s="7" t="n"/>
-      <c r="W6" s="7" t="n"/>
-      <c r="X6" s="7" t="n"/>
-      <c r="Y6" s="7" t="n"/>
-      <c r="Z6" s="7" t="n"/>
-      <c r="AA6" s="7" t="n">
+      <c r="N6" s="10" t="n"/>
+      <c r="O6" s="10" t="n"/>
+      <c r="P6" s="10" t="n"/>
+      <c r="Q6" s="10" t="n"/>
+      <c r="R6" s="10" t="n"/>
+      <c r="S6" s="10" t="n"/>
+      <c r="T6" s="10" t="n"/>
+      <c r="U6" s="10" t="n"/>
+      <c r="V6" s="10" t="n"/>
+      <c r="W6" s="10" t="n"/>
+      <c r="X6" s="10" t="n"/>
+      <c r="Y6" s="10" t="n"/>
+      <c r="Z6" s="10" t="n"/>
+      <c r="AA6" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="AB6" s="7" t="n">
+      <c r="AB6" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="AC6" s="7" t="n"/>
-      <c r="AD6" s="7" t="n"/>
-      <c r="AE6" s="7" t="n"/>
-      <c r="AF6" s="7" t="n"/>
-      <c r="AG6" s="7" t="n"/>
-      <c r="AH6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" s="7" t="n">
+      <c r="AC6" s="10" t="n"/>
+      <c r="AD6" s="10" t="n"/>
+      <c r="AE6" s="10" t="n"/>
+      <c r="AF6" s="10" t="n"/>
+      <c r="AG6" s="10" t="n"/>
+      <c r="AH6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>赖氨酸(98%)</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>氨基酸添加剂</t>
         </is>
       </c>
-      <c r="D7" s="8" t="n"/>
-      <c r="E7" s="8" t="n"/>
-      <c r="F7" s="8" t="n"/>
-      <c r="G7" s="8" t="n"/>
-      <c r="H7" s="8" t="n"/>
-      <c r="I7" s="8" t="n"/>
-      <c r="J7" s="8" t="n"/>
-      <c r="K7" s="8" t="n"/>
-      <c r="L7" s="8" t="n"/>
-      <c r="M7" s="8" t="n"/>
-      <c r="N7" s="8" t="n"/>
-      <c r="O7" s="8" t="n"/>
-      <c r="P7" s="8" t="n"/>
-      <c r="Q7" s="8" t="n">
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="10" t="n"/>
+      <c r="G7" s="10" t="n"/>
+      <c r="H7" s="10" t="n"/>
+      <c r="I7" s="10" t="n"/>
+      <c r="J7" s="10" t="n"/>
+      <c r="K7" s="10" t="n"/>
+      <c r="L7" s="10" t="n"/>
+      <c r="M7" s="10" t="n"/>
+      <c r="N7" s="10" t="n"/>
+      <c r="O7" s="10" t="n"/>
+      <c r="P7" s="10" t="n"/>
+      <c r="Q7" s="10" t="n">
         <v>78</v>
       </c>
-      <c r="R7" s="8" t="n"/>
-      <c r="S7" s="8" t="n"/>
-      <c r="T7" s="8" t="n"/>
-      <c r="U7" s="8" t="n"/>
-      <c r="V7" s="8" t="n"/>
-      <c r="W7" s="8" t="n"/>
-      <c r="X7" s="8" t="n"/>
-      <c r="Y7" s="8" t="n"/>
-      <c r="Z7" s="8" t="n"/>
-      <c r="AA7" s="8" t="n">
+      <c r="R7" s="10" t="n"/>
+      <c r="S7" s="10" t="n"/>
+      <c r="T7" s="10" t="n"/>
+      <c r="U7" s="10" t="n"/>
+      <c r="V7" s="10" t="n"/>
+      <c r="W7" s="10" t="n"/>
+      <c r="X7" s="10" t="n"/>
+      <c r="Y7" s="10" t="n"/>
+      <c r="Z7" s="10" t="n"/>
+      <c r="AA7" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="AB7" s="8" t="n">
+      <c r="AB7" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="AC7" s="8" t="n"/>
-      <c r="AD7" s="8" t="n"/>
-      <c r="AE7" s="8" t="n"/>
-      <c r="AF7" s="8" t="n"/>
-      <c r="AG7" s="8" t="n"/>
-      <c r="AH7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" s="8" t="n">
+      <c r="AC7" s="10" t="n"/>
+      <c r="AD7" s="10" t="n"/>
+      <c r="AE7" s="10" t="n"/>
+      <c r="AF7" s="10" t="n"/>
+      <c r="AG7" s="10" t="n"/>
+      <c r="AH7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>磷酸氢钙</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="10" t="n">
         <v>1.2</v>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>矿物质饲料</t>
         </is>
       </c>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="7" t="n"/>
-      <c r="I8" s="7" t="n"/>
-      <c r="J8" s="7" t="n"/>
-      <c r="K8" s="7" t="n"/>
-      <c r="L8" s="7" t="n"/>
-      <c r="M8" s="7" t="n">
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="10" t="n"/>
+      <c r="F8" s="10" t="n"/>
+      <c r="G8" s="10" t="n"/>
+      <c r="H8" s="10" t="n"/>
+      <c r="I8" s="10" t="n"/>
+      <c r="J8" s="10" t="n"/>
+      <c r="K8" s="10" t="n"/>
+      <c r="L8" s="10" t="n"/>
+      <c r="M8" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="N8" s="7" t="n">
+      <c r="N8" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="O8" s="7" t="n">
+      <c r="O8" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="P8" s="7" t="n"/>
-      <c r="Q8" s="7" t="n"/>
-      <c r="R8" s="7" t="n"/>
-      <c r="S8" s="7" t="n"/>
-      <c r="T8" s="7" t="n"/>
-      <c r="U8" s="7" t="n"/>
-      <c r="V8" s="7" t="n"/>
-      <c r="W8" s="7" t="n"/>
-      <c r="X8" s="7" t="n"/>
-      <c r="Y8" s="7" t="n"/>
-      <c r="Z8" s="7" t="n"/>
-      <c r="AA8" s="7" t="n">
+      <c r="P8" s="10" t="n"/>
+      <c r="Q8" s="10" t="n"/>
+      <c r="R8" s="10" t="n"/>
+      <c r="S8" s="10" t="n"/>
+      <c r="T8" s="10" t="n"/>
+      <c r="U8" s="10" t="n"/>
+      <c r="V8" s="10" t="n"/>
+      <c r="W8" s="10" t="n"/>
+      <c r="X8" s="10" t="n"/>
+      <c r="Y8" s="10" t="n"/>
+      <c r="Z8" s="10" t="n"/>
+      <c r="AA8" s="10" t="n">
         <v>96</v>
       </c>
-      <c r="AB8" s="7" t="n">
+      <c r="AB8" s="10" t="n">
         <v>96</v>
       </c>
-      <c r="AC8" s="7" t="n"/>
-      <c r="AD8" s="7" t="n"/>
-      <c r="AE8" s="7" t="n"/>
-      <c r="AF8" s="7" t="n"/>
-      <c r="AG8" s="7" t="n"/>
-      <c r="AH8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" s="7" t="n">
+      <c r="AC8" s="10" t="n"/>
+      <c r="AD8" s="10" t="n"/>
+      <c r="AE8" s="10" t="n"/>
+      <c r="AF8" s="10" t="n"/>
+      <c r="AG8" s="10" t="n"/>
+      <c r="AH8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>食盐</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n">
+      <c r="B9" s="10" t="n">
         <v>0.8</v>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>矿物质饲料</t>
         </is>
       </c>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="8" t="n"/>
-      <c r="F9" s="8" t="n"/>
-      <c r="G9" s="8" t="n"/>
-      <c r="H9" s="8" t="n"/>
-      <c r="I9" s="8" t="n"/>
-      <c r="J9" s="8" t="n"/>
-      <c r="K9" s="8" t="n"/>
-      <c r="L9" s="8" t="n"/>
-      <c r="M9" s="8" t="n"/>
-      <c r="N9" s="8" t="n"/>
-      <c r="O9" s="8" t="n"/>
-      <c r="P9" s="8" t="n">
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="n"/>
+      <c r="I9" s="10" t="n"/>
+      <c r="J9" s="10" t="n"/>
+      <c r="K9" s="10" t="n"/>
+      <c r="L9" s="10" t="n"/>
+      <c r="M9" s="10" t="n"/>
+      <c r="N9" s="10" t="n"/>
+      <c r="O9" s="10" t="n"/>
+      <c r="P9" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="Q9" s="8" t="n"/>
-      <c r="R9" s="8" t="n"/>
-      <c r="S9" s="8" t="n"/>
-      <c r="T9" s="8" t="n"/>
-      <c r="U9" s="8" t="n"/>
-      <c r="V9" s="8" t="n"/>
-      <c r="W9" s="8" t="n"/>
-      <c r="X9" s="8" t="n"/>
-      <c r="Y9" s="8" t="n"/>
-      <c r="Z9" s="8" t="n"/>
-      <c r="AA9" s="8" t="n">
+      <c r="Q9" s="10" t="n"/>
+      <c r="R9" s="10" t="n"/>
+      <c r="S9" s="10" t="n"/>
+      <c r="T9" s="10" t="n"/>
+      <c r="U9" s="10" t="n"/>
+      <c r="V9" s="10" t="n"/>
+      <c r="W9" s="10" t="n"/>
+      <c r="X9" s="10" t="n"/>
+      <c r="Y9" s="10" t="n"/>
+      <c r="Z9" s="10" t="n"/>
+      <c r="AA9" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="AB9" s="8" t="n">
+      <c r="AB9" s="10" t="n">
         <v>99</v>
       </c>
-      <c r="AC9" s="8" t="n"/>
-      <c r="AD9" s="8" t="n"/>
-      <c r="AE9" s="8" t="n"/>
-      <c r="AF9" s="8" t="n"/>
-      <c r="AG9" s="8" t="n"/>
-      <c r="AH9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" s="8" t="n">
+      <c r="AC9" s="10" t="n"/>
+      <c r="AD9" s="10" t="n"/>
+      <c r="AE9" s="10" t="n"/>
+      <c r="AF9" s="10" t="n"/>
+      <c r="AG9" s="10" t="n"/>
+      <c r="AH9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" s="10" t="n">
         <v>0</v>
       </c>
     </row>
